--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/TENNESSEE_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/TENNESSEE_2021.xlsx
@@ -3127,7 +3127,7 @@
         <v>10</v>
       </c>
       <c r="D154">
-        <v>0.0009819324430479183</v>
+        <v>0.0009819324430479185</v>
       </c>
     </row>
     <row r="155">
@@ -3217,7 +3217,7 @@
         <v>10</v>
       </c>
       <c r="D159">
-        <v>0.0009819324430479183</v>
+        <v>0.0009819324430479185</v>
       </c>
     </row>
     <row r="160">
@@ -3739,7 +3739,7 @@
         <v>10</v>
       </c>
       <c r="D188">
-        <v>0.0009819324430479183</v>
+        <v>0.0009819324430479185</v>
       </c>
     </row>
     <row r="189">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C256">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C266">
@@ -6439,7 +6439,7 @@
         <v>10</v>
       </c>
       <c r="D338">
-        <v>0.0009819324430479183</v>
+        <v>0.0009819324430479185</v>
       </c>
     </row>
     <row r="339">
@@ -6637,7 +6637,7 @@
         <v>10</v>
       </c>
       <c r="D349">
-        <v>0.0009819324430479183</v>
+        <v>0.0009819324430479185</v>
       </c>
     </row>
     <row r="350">
@@ -7267,7 +7267,7 @@
         <v>10</v>
       </c>
       <c r="D384">
-        <v>0.0009819324430479183</v>
+        <v>0.0009819324430479185</v>
       </c>
     </row>
     <row r="385">
@@ -9247,7 +9247,7 @@
         <v>10</v>
       </c>
       <c r="D494">
-        <v>0.0009819324430479183</v>
+        <v>0.0009819324430479185</v>
       </c>
     </row>
     <row r="495">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C701">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C702">
@@ -13614,14 +13614,14 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C737">
         <v>10</v>
       </c>
       <c r="D737">
-        <v>0.0009819324430479183</v>
+        <v>0.0009819324430479185</v>
       </c>
     </row>
     <row r="738">
@@ -13639,7 +13639,7 @@
         <v>99</v>
       </c>
       <c r="D738">
-        <v>0.009721131186174391</v>
+        <v>0.009721131186174393</v>
       </c>
     </row>
     <row r="739">
@@ -13740,7 +13740,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C744">
@@ -14035,7 +14035,7 @@
         <v>10</v>
       </c>
       <c r="D760">
-        <v>0.0009819324430479183</v>
+        <v>0.0009819324430479185</v>
       </c>
     </row>
     <row r="761">
@@ -14611,7 +14611,7 @@
         <v>10</v>
       </c>
       <c r="D792">
-        <v>0.0009819324430479183</v>
+        <v>0.0009819324430479185</v>
       </c>
     </row>
     <row r="793">
@@ -16735,7 +16735,7 @@
         <v>10</v>
       </c>
       <c r="D910">
-        <v>0.0009819324430479183</v>
+        <v>0.0009819324430479185</v>
       </c>
     </row>
     <row r="911">
@@ -16915,7 +16915,7 @@
         <v>10</v>
       </c>
       <c r="D920">
-        <v>0.0009819324430479183</v>
+        <v>0.0009819324430479185</v>
       </c>
     </row>
     <row r="921">
@@ -18877,7 +18877,7 @@
         <v>10</v>
       </c>
       <c r="D1029">
-        <v>0.0009819324430479183</v>
+        <v>0.0009819324430479185</v>
       </c>
     </row>
     <row r="1030">
@@ -19212,7 +19212,7 @@
       </c>
       <c r="B1048" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1048">
@@ -21397,7 +21397,7 @@
         <v>10</v>
       </c>
       <c r="D1169">
-        <v>0.0009819324430479183</v>
+        <v>0.0009819324430479185</v>
       </c>
     </row>
     <row r="1170">
@@ -21469,7 +21469,7 @@
         <v>10</v>
       </c>
       <c r="D1173">
-        <v>0.0009819324430479183</v>
+        <v>0.0009819324430479185</v>
       </c>
     </row>
     <row r="1174">
